--- a/labelled_sheets/2026_07_24_generalisation_relabel_farm_and_image_balliang.xlsx
+++ b/labelled_sheets/2026_07_24_generalisation_relabel_farm_and_image_balliang.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="530" documentId="11_90A4FCAEB2F87010E270F30525BF9FD238A46EF1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F79F79AA-37C6-4AB8-9E96-A24D8EF99E21}"/>
+  <xr:revisionPtr revIDLastSave="531" documentId="11_90A4FCAEB2F87010E270F30525BF9FD238A46EF1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C48EB667-98FC-4999-8243-EE1D9D2A1B98}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Farm labels" sheetId="1" r:id="rId1"/>
@@ -1431,7 +1431,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1451,12 +1451,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1624,7 +1618,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -12371,6 +12365,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="73cbf0c7-d69e-427c-8bf4-4bd79e720451" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="94707517-fcf5-48ba-971e-d38caecd4d61">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C2D78CD4D7E5E443850520BD8D915EF0" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="75ad294e393f4787ac547a5ae7fd66fe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="94707517-fcf5-48ba-971e-d38caecd4d61" xmlns:ns3="73cbf0c7-d69e-427c-8bf4-4bd79e720451" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="396587b85e5f7bdb019044cddbd799be" ns2:_="" ns3:_="">
     <xsd:import namespace="94707517-fcf5-48ba-971e-d38caecd4d61"/>
@@ -12571,28 +12585,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="73cbf0c7-d69e-427c-8bf4-4bd79e720451" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="94707517-fcf5-48ba-971e-d38caecd4d61">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36960A3B-12DD-4D78-923C-EBB20E67CDF7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF7A7B24-5427-4277-ADA2-44BF47BB589F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12600,5 +12594,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF7A7B24-5427-4277-ADA2-44BF47BB589F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36960A3B-12DD-4D78-923C-EBB20E67CDF7}"/>
 </file>
--- a/labelled_sheets/2026_07_24_generalisation_relabel_farm_and_image_balliang.xlsx
+++ b/labelled_sheets/2026_07_24_generalisation_relabel_farm_and_image_balliang.xlsx
@@ -599,8 +599,8 @@
   <dimension ref="A1:AE66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="19.42578125" customWidth="1" min="2" max="2"/>
+    <col width="19.42578125" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="10.7109375" customWidth="1" min="3" max="3"/>
     <col width="44.42578125" customWidth="1" min="4" max="4"/>
     <col width="8.85546875" customWidth="1" min="5" max="5"/>
@@ -629,12 +629,12 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Farm UID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -786,12 +786,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
           <t>farm-e64475f1a639289c</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
@@ -859,12 +859,12 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
           <t>farm-87f9435d6cc3c9bf</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -928,12 +928,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
           <t>farm-14af52479742e8bd</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -997,12 +997,12 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
           <t>farm-746099f5af1c53cf</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -1066,12 +1066,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
           <t>farm-5ace19487f310dc7</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
@@ -1143,12 +1143,12 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
           <t>farm-659df1a466ff33a9</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
@@ -1212,12 +1212,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
           <t>farm-0299228132457c96</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
@@ -1281,12 +1281,12 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
           <t>farm-20f020a0394ede4a</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
@@ -1358,12 +1358,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
           <t>farm-b1f060732da67c50</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
@@ -1423,12 +1423,12 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
           <t>farm-b3839e9b51b3269f</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
@@ -1492,12 +1492,12 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
           <t>farm-485ae49bdbfa2757</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
@@ -1561,12 +1561,12 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
           <t>farm-9d0494ef5f7061ae</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
@@ -1626,12 +1626,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
           <t>farm-7f6266d67fc7b292</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -1695,12 +1695,12 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
           <t>farm-5bf71a6c96a00159</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
@@ -1760,12 +1760,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
           <t>farm-c69f5b74e1637d55</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
@@ -1829,12 +1829,12 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
           <t>farm-074508abc6ddc165</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
@@ -1898,12 +1898,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
           <t>farm-10e0e10d7e432e27</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
@@ -1967,12 +1967,12 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
           <t>farm-4836fb36b16ea574</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
@@ -2036,12 +2036,12 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
           <t>farm-8c253c3366bd8dd3</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
@@ -2105,12 +2105,12 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
           <t>farm-eb01786a135457e2</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
@@ -2174,12 +2174,12 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
           <t>farm-96f434662b14a10a</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
@@ -2243,12 +2243,12 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
           <t>farm-03077a0bf601b68b</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -2312,12 +2312,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
           <t>farm-60d5c49cdf02db44</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
@@ -2381,12 +2381,12 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
           <t>farm-0bbbf4cd36511697</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
@@ -2450,12 +2450,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
           <t>farm-06a5a2cd01ac6ca6</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
@@ -2519,12 +2519,12 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
           <t>farm-8ac3946e63325413</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
@@ -2588,12 +2588,12 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
           <t>farm-f00e1026452af8b0</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
@@ -2657,12 +2657,12 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
           <t>farm-6f2e8f0ed6d9258d</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
@@ -2726,12 +2726,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
           <t>farm-11bf1a5a2f4bb6c0</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
@@ -2795,12 +2795,12 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
           <t>farm-855c73c59a076d71</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
@@ -2872,12 +2872,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
           <t>farm-3a378a1add1f62f4</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
@@ -2941,12 +2941,12 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
           <t>farm-1262b748b8bc7ff1</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
@@ -3010,12 +3010,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
           <t>farm-41cc748fca915349</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
@@ -3079,12 +3079,12 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
           <t>farm-3563fa367eab3a43</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -3148,12 +3148,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
           <t>farm-e9ff000a94a89b1a</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
@@ -3217,12 +3217,12 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
           <t>farm-c67269d4e8d60f7f</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
@@ -3286,12 +3286,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
           <t>farm-4f40e72b299c318e</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
@@ -3355,12 +3355,12 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
           <t>farm-725704fb1a245f80</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
@@ -3424,12 +3424,12 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
           <t>farm-f59247274bd2496c</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
@@ -3489,12 +3489,12 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
           <t>farm-f6b038da5dd7dc75</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
@@ -3566,12 +3566,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
           <t>farm-1c7d9a0111ecf572</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
@@ -3635,12 +3635,12 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
           <t>farm-c49b19e235e2b061</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
@@ -3712,12 +3712,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
           <t>farm-9a61b6a17f97ba72</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
@@ -3789,12 +3789,12 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
           <t>farm-0dbf3bd5fa5b6f36</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
@@ -3858,12 +3858,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
           <t>farm-3f8574c5694d1cf0</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
@@ -3927,12 +3927,12 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
           <t>farm-b0db552916b2cd10</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
@@ -3996,12 +3996,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
           <t>farm-57a8d7f843c38504</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
@@ -4065,12 +4065,12 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
           <t>farm-856d7e3cc18639c7</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
@@ -4130,12 +4130,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
           <t>farm-383f63e3f7a7da24</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
@@ -4199,12 +4199,12 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
           <t>farm-ff3ff9a555d745f4</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
@@ -4276,12 +4276,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
           <t>farm-5ccdcf7255ce0473</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
@@ -4345,12 +4345,12 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
           <t>farm-2736bad424a20cd6</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
@@ -4414,12 +4414,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
           <t>farm-639c9d17e71d07f4</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
@@ -4491,12 +4491,12 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
           <t>farm-1c62e112fe6b88cb</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
@@ -4560,12 +4560,12 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
           <t>farm-68cf2cfdbb044e86</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
@@ -4629,12 +4629,12 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
           <t>farm-719054ad3fa7a13a</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
@@ -4694,12 +4694,12 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
           <t>farm-cd1a7ad828e59ca2</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
@@ -4759,12 +4759,12 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
           <t>farm-ec87e85565cbba3c</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
@@ -4824,12 +4824,12 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
           <t>farm-06f2c6829a4bd5fc</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
@@ -4901,12 +4901,12 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
           <t>farm-05270ec8c18c39ef</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
@@ -4970,12 +4970,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
           <t>farm-4564e66abc59f856</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
@@ -5039,12 +5039,12 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
           <t>farm-e83db331287bbc87</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
@@ -5116,12 +5116,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
           <t>farm-ce9a0c36aa3a1370</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
@@ -5185,12 +5185,12 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
           <t>farm-681881e6608d6b6d</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
@@ -5254,12 +5254,12 @@
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
           <t>farm-2de1bf871636377b</t>
-        </is>
-      </c>
-      <c r="B66" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C66" s="12" t="n">
@@ -5339,8 +5339,8 @@
   <dimension ref="A1:H325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="20.7109375" customWidth="1" min="2" max="2"/>
+    <col width="20.7109375" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="13.42578125" customWidth="1" min="3" max="3"/>
     <col width="45.85546875" customWidth="1" min="4" max="4"/>
     <col width="9.7109375" customWidth="1" min="5" max="5"/>
@@ -5352,12 +5352,12 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Farm UID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -5394,12 +5394,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
           <t>farm-e64475f1a639289c</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
@@ -5430,12 +5430,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
           <t>farm-e64475f1a639289c</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
@@ -5466,12 +5466,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
           <t>farm-e64475f1a639289c</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -5502,12 +5502,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
           <t>farm-e64475f1a639289c</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
@@ -5538,12 +5538,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
           <t>farm-e64475f1a639289c</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
@@ -5574,12 +5574,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
           <t>farm-e64475f1a639289c</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
@@ -5610,12 +5610,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
           <t>farm-e64475f1a639289c</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
@@ -5646,12 +5646,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
           <t>farm-e64475f1a639289c</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
@@ -5682,12 +5682,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
           <t>farm-e64475f1a639289c</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
@@ -5718,12 +5718,12 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
           <t>farm-e64475f1a639289c</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
@@ -5754,12 +5754,12 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
           <t>farm-87f9435d6cc3c9bf</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
@@ -5790,12 +5790,12 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
           <t>farm-87f9435d6cc3c9bf</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
@@ -5826,12 +5826,12 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
           <t>farm-87f9435d6cc3c9bf</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
@@ -5862,12 +5862,12 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
           <t>farm-87f9435d6cc3c9bf</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
@@ -5898,12 +5898,12 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
           <t>farm-87f9435d6cc3c9bf</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
@@ -5934,12 +5934,12 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
           <t>farm-87f9435d6cc3c9bf</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
@@ -5970,12 +5970,12 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
           <t>farm-87f9435d6cc3c9bf</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C18" s="16" t="n">
@@ -6006,12 +6006,12 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
           <t>farm-14af52479742e8bd</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
@@ -6042,12 +6042,12 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
           <t>farm-746099f5af1c53cf</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C20" s="16" t="n">
@@ -6078,12 +6078,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
           <t>farm-5ace19487f310dc7</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
@@ -6114,12 +6114,12 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
           <t>farm-5ace19487f310dc7</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
@@ -6150,12 +6150,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
           <t>farm-5ace19487f310dc7</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
@@ -6186,12 +6186,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
           <t>farm-5ace19487f310dc7</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
@@ -6222,12 +6222,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
           <t>farm-5ace19487f310dc7</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
@@ -6258,12 +6258,12 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
           <t>farm-5ace19487f310dc7</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C26" s="12" t="n">
@@ -6294,12 +6294,12 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
           <t>farm-659df1a466ff33a9</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
@@ -6330,12 +6330,12 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
           <t>farm-659df1a466ff33a9</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
@@ -6366,12 +6366,12 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
           <t>farm-659df1a466ff33a9</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
@@ -6402,12 +6402,12 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
           <t>farm-659df1a466ff33a9</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
@@ -6438,12 +6438,12 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
           <t>farm-659df1a466ff33a9</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
@@ -6474,12 +6474,12 @@
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
           <t>farm-659df1a466ff33a9</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C32" s="16" t="n">
@@ -6510,12 +6510,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
           <t>farm-0299228132457c96</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
@@ -6546,12 +6546,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
           <t>farm-0299228132457c96</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
@@ -6582,12 +6582,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
           <t>farm-0299228132457c96</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
@@ -6618,12 +6618,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
           <t>farm-0299228132457c96</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
@@ -6654,12 +6654,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
           <t>farm-0299228132457c96</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
@@ -6690,12 +6690,12 @@
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
           <t>farm-0299228132457c96</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C38" s="12" t="n">
@@ -6726,12 +6726,12 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
           <t>farm-20f020a0394ede4a</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
@@ -6762,12 +6762,12 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
           <t>farm-20f020a0394ede4a</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
@@ -6798,12 +6798,12 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
           <t>farm-20f020a0394ede4a</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
@@ -6834,12 +6834,12 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
           <t>farm-20f020a0394ede4a</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
@@ -6870,12 +6870,12 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
           <t>farm-20f020a0394ede4a</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
@@ -6906,12 +6906,12 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
           <t>farm-20f020a0394ede4a</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
@@ -6942,12 +6942,12 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
           <t>farm-20f020a0394ede4a</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
@@ -6978,12 +6978,12 @@
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
           <t>farm-20f020a0394ede4a</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C46" s="16" t="n">
@@ -7014,12 +7014,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
           <t>farm-b1f060732da67c50</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
@@ -7050,12 +7050,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
           <t>farm-b1f060732da67c50</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
@@ -7086,12 +7086,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
           <t>farm-b1f060732da67c50</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
@@ -7122,12 +7122,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
           <t>farm-b1f060732da67c50</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
@@ -7158,12 +7158,12 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
           <t>farm-b1f060732da67c50</t>
-        </is>
-      </c>
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C51" s="12" t="n">
@@ -7194,12 +7194,12 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
           <t>farm-b3839e9b51b3269f</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
@@ -7230,12 +7230,12 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
           <t>farm-b3839e9b51b3269f</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
@@ -7266,12 +7266,12 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
           <t>farm-b3839e9b51b3269f</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
@@ -7302,12 +7302,12 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
           <t>farm-b3839e9b51b3269f</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
@@ -7338,12 +7338,12 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
           <t>farm-b3839e9b51b3269f</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
@@ -7374,12 +7374,12 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
           <t>farm-b3839e9b51b3269f</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
@@ -7410,12 +7410,12 @@
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
           <t>farm-b3839e9b51b3269f</t>
-        </is>
-      </c>
-      <c r="B58" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C58" s="16" t="n">
@@ -7446,12 +7446,12 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
           <t>farm-485ae49bdbfa2757</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
@@ -7482,12 +7482,12 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
           <t>farm-485ae49bdbfa2757</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
@@ -7518,12 +7518,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
           <t>farm-485ae49bdbfa2757</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
@@ -7554,12 +7554,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
           <t>farm-485ae49bdbfa2757</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
@@ -7590,12 +7590,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
           <t>farm-485ae49bdbfa2757</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
@@ -7626,12 +7626,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
           <t>farm-485ae49bdbfa2757</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
@@ -7662,12 +7662,12 @@
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
           <t>farm-485ae49bdbfa2757</t>
-        </is>
-      </c>
-      <c r="B65" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C65" s="12" t="n">
@@ -7698,12 +7698,12 @@
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
           <t>farm-9d0494ef5f7061ae</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -7734,12 +7734,12 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
           <t>farm-9d0494ef5f7061ae</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -7770,12 +7770,12 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
           <t>farm-9d0494ef5f7061ae</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
@@ -7806,12 +7806,12 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
           <t>farm-9d0494ef5f7061ae</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
@@ -7842,12 +7842,12 @@
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
           <t>farm-9d0494ef5f7061ae</t>
-        </is>
-      </c>
-      <c r="B70" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C70" s="16" t="n">
@@ -7878,12 +7878,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
           <t>farm-7f6266d67fc7b292</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
@@ -7914,12 +7914,12 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
           <t>farm-7f6266d67fc7b292</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
@@ -7954,12 +7954,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
           <t>farm-7f6266d67fc7b292</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
@@ -7990,12 +7990,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
           <t>farm-7f6266d67fc7b292</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
@@ -8030,12 +8030,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
           <t>farm-7f6266d67fc7b292</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
@@ -8070,12 +8070,12 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
           <t>farm-7f6266d67fc7b292</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
@@ -8106,12 +8106,12 @@
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
           <t>farm-7f6266d67fc7b292</t>
-        </is>
-      </c>
-      <c r="B77" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C77" s="12" t="n">
@@ -8142,12 +8142,12 @@
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
           <t>farm-5bf71a6c96a00159</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
@@ -8182,12 +8182,12 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
           <t>farm-5bf71a6c96a00159</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
@@ -8218,12 +8218,12 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
           <t>farm-5bf71a6c96a00159</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
@@ -8254,12 +8254,12 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
           <t>farm-5bf71a6c96a00159</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
@@ -8290,12 +8290,12 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
           <t>farm-5bf71a6c96a00159</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
@@ -8326,12 +8326,12 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
           <t>farm-5bf71a6c96a00159</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -8362,12 +8362,12 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
           <t>farm-5bf71a6c96a00159</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
@@ -8398,12 +8398,12 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
           <t>farm-5bf71a6c96a00159</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
@@ -8434,12 +8434,12 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
           <t>farm-5bf71a6c96a00159</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C86" s="8" t="n">
@@ -8470,12 +8470,12 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
           <t>farm-5bf71a6c96a00159</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
@@ -8506,12 +8506,12 @@
     <row r="88">
       <c r="A88" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B88" s="16" t="inlineStr">
+        <is>
           <t>farm-5bf71a6c96a00159</t>
-        </is>
-      </c>
-      <c r="B88" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C88" s="16" t="n">
@@ -8542,12 +8542,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
           <t>farm-c69f5b74e1637d55</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
@@ -8578,12 +8578,12 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
           <t>farm-c69f5b74e1637d55</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
@@ -8614,12 +8614,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
           <t>farm-c69f5b74e1637d55</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
@@ -8650,12 +8650,12 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
           <t>farm-c69f5b74e1637d55</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
@@ -8686,12 +8686,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
           <t>farm-c69f5b74e1637d55</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
@@ -8722,12 +8722,12 @@
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
           <t>farm-c69f5b74e1637d55</t>
-        </is>
-      </c>
-      <c r="B94" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C94" s="12" t="n">
@@ -8758,12 +8758,12 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
           <t>farm-074508abc6ddc165</t>
-        </is>
-      </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
@@ -8794,12 +8794,12 @@
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
           <t>farm-074508abc6ddc165</t>
-        </is>
-      </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C96" s="8" t="n">
@@ -8830,12 +8830,12 @@
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
           <t>farm-074508abc6ddc165</t>
-        </is>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
@@ -8866,12 +8866,12 @@
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
           <t>farm-074508abc6ddc165</t>
-        </is>
-      </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C98" s="8" t="n">
@@ -8902,12 +8902,12 @@
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
           <t>farm-074508abc6ddc165</t>
-        </is>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
@@ -8938,12 +8938,12 @@
     <row r="100">
       <c r="A100" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B100" s="16" t="inlineStr">
+        <is>
           <t>farm-074508abc6ddc165</t>
-        </is>
-      </c>
-      <c r="B100" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C100" s="16" t="n">
@@ -8974,12 +8974,12 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
           <t>farm-10e0e10d7e432e27</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
@@ -9010,12 +9010,12 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
           <t>farm-10e0e10d7e432e27</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C102" s="4" t="n">
@@ -9046,12 +9046,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
           <t>farm-10e0e10d7e432e27</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
@@ -9082,12 +9082,12 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
           <t>farm-10e0e10d7e432e27</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
@@ -9118,12 +9118,12 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
           <t>farm-10e0e10d7e432e27</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
@@ -9154,12 +9154,12 @@
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
           <t>farm-10e0e10d7e432e27</t>
-        </is>
-      </c>
-      <c r="B106" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C106" s="12" t="n">
@@ -9190,12 +9190,12 @@
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
           <t>farm-4836fb36b16ea574</t>
-        </is>
-      </c>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
@@ -9226,12 +9226,12 @@
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
           <t>farm-4836fb36b16ea574</t>
-        </is>
-      </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C108" s="8" t="n">
@@ -9262,12 +9262,12 @@
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
           <t>farm-4836fb36b16ea574</t>
-        </is>
-      </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
@@ -9298,12 +9298,12 @@
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
           <t>farm-4836fb36b16ea574</t>
-        </is>
-      </c>
-      <c r="B110" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C110" s="8" t="n">
@@ -9334,12 +9334,12 @@
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
           <t>farm-4836fb36b16ea574</t>
-        </is>
-      </c>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
@@ -9370,12 +9370,12 @@
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
           <t>farm-4836fb36b16ea574</t>
-        </is>
-      </c>
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C112" s="8" t="n">
@@ -9406,12 +9406,12 @@
     <row r="113">
       <c r="A113" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B113" s="16" t="inlineStr">
+        <is>
           <t>farm-4836fb36b16ea574</t>
-        </is>
-      </c>
-      <c r="B113" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C113" s="16" t="n">
@@ -9442,12 +9442,12 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
           <t>farm-8c253c3366bd8dd3</t>
-        </is>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
@@ -9478,12 +9478,12 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
           <t>farm-8c253c3366bd8dd3</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
@@ -9514,12 +9514,12 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
           <t>farm-8c253c3366bd8dd3</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
@@ -9550,12 +9550,12 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
           <t>farm-8c253c3366bd8dd3</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C117" s="4" t="n">
@@ -9586,12 +9586,12 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
           <t>farm-8c253c3366bd8dd3</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
@@ -9622,12 +9622,12 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
           <t>farm-8c253c3366bd8dd3</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
@@ -9658,12 +9658,12 @@
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
           <t>farm-8c253c3366bd8dd3</t>
-        </is>
-      </c>
-      <c r="B120" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C120" s="12" t="n">
@@ -9694,12 +9694,12 @@
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
           <t>farm-eb01786a135457e2</t>
-        </is>
-      </c>
-      <c r="B121" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
@@ -9730,12 +9730,12 @@
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
           <t>farm-eb01786a135457e2</t>
-        </is>
-      </c>
-      <c r="B122" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C122" s="8" t="n">
@@ -9766,12 +9766,12 @@
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
           <t>farm-eb01786a135457e2</t>
-        </is>
-      </c>
-      <c r="B123" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
@@ -9802,12 +9802,12 @@
     <row r="124">
       <c r="A124" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B124" s="16" t="inlineStr">
+        <is>
           <t>farm-eb01786a135457e2</t>
-        </is>
-      </c>
-      <c r="B124" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C124" s="16" t="n">
@@ -9838,12 +9838,12 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
           <t>farm-96f434662b14a10a</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
@@ -9874,12 +9874,12 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
           <t>farm-96f434662b14a10a</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C126" s="4" t="n">
@@ -9910,12 +9910,12 @@
     <row r="127">
       <c r="A127" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
           <t>farm-96f434662b14a10a</t>
-        </is>
-      </c>
-      <c r="B127" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C127" s="12" t="n">
@@ -9946,12 +9946,12 @@
     <row r="128">
       <c r="A128" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B128" s="16" t="inlineStr">
+        <is>
           <t>farm-03077a0bf601b68b</t>
-        </is>
-      </c>
-      <c r="B128" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C128" s="16" t="n">
@@ -9982,12 +9982,12 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
           <t>farm-60d5c49cdf02db44</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C129" s="4" t="n">
@@ -10018,12 +10018,12 @@
     <row r="130">
       <c r="A130" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="inlineStr">
+        <is>
           <t>farm-60d5c49cdf02db44</t>
-        </is>
-      </c>
-      <c r="B130" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C130" s="12" t="n">
@@ -10054,12 +10054,12 @@
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B131" s="8" t="inlineStr">
+        <is>
           <t>farm-0bbbf4cd36511697</t>
-        </is>
-      </c>
-      <c r="B131" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C131" s="8" t="n">
@@ -10090,12 +10090,12 @@
     <row r="132">
       <c r="A132" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B132" s="16" t="inlineStr">
+        <is>
           <t>farm-0bbbf4cd36511697</t>
-        </is>
-      </c>
-      <c r="B132" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C132" s="16" t="n">
@@ -10126,12 +10126,12 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
           <t>farm-06a5a2cd01ac6ca6</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C133" s="4" t="n">
@@ -10162,12 +10162,12 @@
     <row r="134">
       <c r="A134" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B134" s="12" t="inlineStr">
+        <is>
           <t>farm-06a5a2cd01ac6ca6</t>
-        </is>
-      </c>
-      <c r="B134" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C134" s="12" t="n">
@@ -10202,12 +10202,12 @@
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="inlineStr">
+        <is>
           <t>farm-8ac3946e63325413</t>
-        </is>
-      </c>
-      <c r="B135" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
@@ -10238,12 +10238,12 @@
     <row r="136">
       <c r="A136" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B136" s="16" t="inlineStr">
+        <is>
           <t>farm-8ac3946e63325413</t>
-        </is>
-      </c>
-      <c r="B136" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C136" s="16" t="n">
@@ -10274,12 +10274,12 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
           <t>farm-f00e1026452af8b0</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C137" s="4" t="n">
@@ -10310,12 +10310,12 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
           <t>farm-f00e1026452af8b0</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C138" s="4" t="n">
@@ -10346,12 +10346,12 @@
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="inlineStr">
+        <is>
           <t>farm-f00e1026452af8b0</t>
-        </is>
-      </c>
-      <c r="B139" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C139" s="12" t="n">
@@ -10382,12 +10382,12 @@
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
           <t>farm-6f2e8f0ed6d9258d</t>
-        </is>
-      </c>
-      <c r="B140" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C140" s="8" t="n">
@@ -10418,12 +10418,12 @@
     <row r="141">
       <c r="A141" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B141" s="16" t="inlineStr">
+        <is>
           <t>farm-6f2e8f0ed6d9258d</t>
-        </is>
-      </c>
-      <c r="B141" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C141" s="16" t="n">
@@ -10454,12 +10454,12 @@
     <row r="142">
       <c r="A142" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B142" s="12" t="inlineStr">
+        <is>
           <t>farm-11bf1a5a2f4bb6c0</t>
-        </is>
-      </c>
-      <c r="B142" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C142" s="12" t="n">
@@ -10490,12 +10490,12 @@
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="inlineStr">
+        <is>
           <t>farm-855c73c59a076d71</t>
-        </is>
-      </c>
-      <c r="B143" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
@@ -10526,12 +10526,12 @@
     <row r="144">
       <c r="A144" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B144" s="16" t="inlineStr">
+        <is>
           <t>farm-855c73c59a076d71</t>
-        </is>
-      </c>
-      <c r="B144" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C144" s="16" t="n">
@@ -10562,12 +10562,12 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
           <t>farm-3a378a1add1f62f4</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C145" s="4" t="n">
@@ -10598,12 +10598,12 @@
     <row r="146">
       <c r="A146" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B146" s="12" t="inlineStr">
+        <is>
           <t>farm-3a378a1add1f62f4</t>
-        </is>
-      </c>
-      <c r="B146" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C146" s="12" t="n">
@@ -10634,12 +10634,12 @@
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="inlineStr">
+        <is>
           <t>farm-1262b748b8bc7ff1</t>
-        </is>
-      </c>
-      <c r="B147" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
@@ -10670,12 +10670,12 @@
     <row r="148">
       <c r="A148" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B148" s="16" t="inlineStr">
+        <is>
           <t>farm-1262b748b8bc7ff1</t>
-        </is>
-      </c>
-      <c r="B148" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C148" s="16" t="n">
@@ -10706,12 +10706,12 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
           <t>farm-41cc748fca915349</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C149" s="4" t="n">
@@ -10742,12 +10742,12 @@
     <row r="150">
       <c r="A150" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B150" s="12" t="inlineStr">
+        <is>
           <t>farm-41cc748fca915349</t>
-        </is>
-      </c>
-      <c r="B150" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C150" s="12" t="n">
@@ -10778,12 +10778,12 @@
     <row r="151">
       <c r="A151" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B151" s="16" t="inlineStr">
+        <is>
           <t>farm-3563fa367eab3a43</t>
-        </is>
-      </c>
-      <c r="B151" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C151" s="16" t="n">
@@ -10814,12 +10814,12 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
           <t>farm-e9ff000a94a89b1a</t>
-        </is>
-      </c>
-      <c r="B152" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C152" s="4" t="n">
@@ -10850,12 +10850,12 @@
     <row r="153">
       <c r="A153" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="inlineStr">
+        <is>
           <t>farm-e9ff000a94a89b1a</t>
-        </is>
-      </c>
-      <c r="B153" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C153" s="12" t="n">
@@ -10886,12 +10886,12 @@
     <row r="154">
       <c r="A154" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
           <t>farm-c67269d4e8d60f7f</t>
-        </is>
-      </c>
-      <c r="B154" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C154" s="8" t="n">
@@ -10922,12 +10922,12 @@
     <row r="155">
       <c r="A155" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B155" s="16" t="inlineStr">
+        <is>
           <t>farm-c67269d4e8d60f7f</t>
-        </is>
-      </c>
-      <c r="B155" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C155" s="16" t="n">
@@ -10958,12 +10958,12 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
           <t>farm-4f40e72b299c318e</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C156" s="4" t="n">
@@ -10994,12 +10994,12 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
           <t>farm-4f40e72b299c318e</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C157" s="4" t="n">
@@ -11030,12 +11030,12 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
           <t>farm-4f40e72b299c318e</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C158" s="4" t="n">
@@ -11066,12 +11066,12 @@
     <row r="159">
       <c r="A159" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B159" s="12" t="inlineStr">
+        <is>
           <t>farm-4f40e72b299c318e</t>
-        </is>
-      </c>
-      <c r="B159" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C159" s="12" t="n">
@@ -11102,12 +11102,12 @@
     <row r="160">
       <c r="A160" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B160" s="8" t="inlineStr">
+        <is>
           <t>farm-725704fb1a245f80</t>
-        </is>
-      </c>
-      <c r="B160" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C160" s="8" t="n">
@@ -11138,12 +11138,12 @@
     <row r="161">
       <c r="A161" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B161" s="16" t="inlineStr">
+        <is>
           <t>farm-725704fb1a245f80</t>
-        </is>
-      </c>
-      <c r="B161" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C161" s="16" t="n">
@@ -11174,12 +11174,12 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
           <t>farm-f59247274bd2496c</t>
-        </is>
-      </c>
-      <c r="B162" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C162" s="4" t="n">
@@ -11210,12 +11210,12 @@
     <row r="163">
       <c r="A163" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B163" s="12" t="inlineStr">
+        <is>
           <t>farm-f59247274bd2496c</t>
-        </is>
-      </c>
-      <c r="B163" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C163" s="12" t="n">
@@ -11246,12 +11246,12 @@
     <row r="164">
       <c r="A164" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B164" s="8" t="inlineStr">
+        <is>
           <t>farm-f6b038da5dd7dc75</t>
-        </is>
-      </c>
-      <c r="B164" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C164" s="8" t="n">
@@ -11282,12 +11282,12 @@
     <row r="165">
       <c r="A165" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B165" s="8" t="inlineStr">
+        <is>
           <t>farm-f6b038da5dd7dc75</t>
-        </is>
-      </c>
-      <c r="B165" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C165" s="8" t="n">
@@ -11318,12 +11318,12 @@
     <row r="166">
       <c r="A166" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B166" s="8" t="inlineStr">
+        <is>
           <t>farm-f6b038da5dd7dc75</t>
-        </is>
-      </c>
-      <c r="B166" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C166" s="8" t="n">
@@ -11354,12 +11354,12 @@
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B167" s="8" t="inlineStr">
+        <is>
           <t>farm-f6b038da5dd7dc75</t>
-        </is>
-      </c>
-      <c r="B167" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C167" s="8" t="n">
@@ -11394,12 +11394,12 @@
     <row r="168">
       <c r="A168" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
           <t>farm-f6b038da5dd7dc75</t>
-        </is>
-      </c>
-      <c r="B168" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C168" s="8" t="n">
@@ -11430,12 +11430,12 @@
     <row r="169">
       <c r="A169" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B169" s="8" t="inlineStr">
+        <is>
           <t>farm-f6b038da5dd7dc75</t>
-        </is>
-      </c>
-      <c r="B169" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C169" s="8" t="n">
@@ -11466,12 +11466,12 @@
     <row r="170">
       <c r="A170" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B170" s="16" t="inlineStr">
+        <is>
           <t>farm-f6b038da5dd7dc75</t>
-        </is>
-      </c>
-      <c r="B170" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C170" s="16" t="n">
@@ -11502,12 +11502,12 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
           <t>farm-1c7d9a0111ecf572</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C171" s="4" t="n">
@@ -11538,12 +11538,12 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
           <t>farm-1c7d9a0111ecf572</t>
-        </is>
-      </c>
-      <c r="B172" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C172" s="4" t="n">
@@ -11574,12 +11574,12 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
           <t>farm-1c7d9a0111ecf572</t>
-        </is>
-      </c>
-      <c r="B173" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C173" s="4" t="n">
@@ -11610,12 +11610,12 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
           <t>farm-1c7d9a0111ecf572</t>
-        </is>
-      </c>
-      <c r="B174" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C174" s="4" t="n">
@@ -11646,12 +11646,12 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
           <t>farm-1c7d9a0111ecf572</t>
-        </is>
-      </c>
-      <c r="B175" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C175" s="4" t="n">
@@ -11682,12 +11682,12 @@
     <row r="176">
       <c r="A176" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B176" s="12" t="inlineStr">
+        <is>
           <t>farm-1c7d9a0111ecf572</t>
-        </is>
-      </c>
-      <c r="B176" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C176" s="12" t="n">
@@ -11718,12 +11718,12 @@
     <row r="177">
       <c r="A177" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B177" s="8" t="inlineStr">
+        <is>
           <t>farm-c49b19e235e2b061</t>
-        </is>
-      </c>
-      <c r="B177" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C177" s="8" t="n">
@@ -11754,12 +11754,12 @@
     <row r="178">
       <c r="A178" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B178" s="8" t="inlineStr">
+        <is>
           <t>farm-c49b19e235e2b061</t>
-        </is>
-      </c>
-      <c r="B178" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C178" s="8" t="n">
@@ -11790,12 +11790,12 @@
     <row r="179">
       <c r="A179" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B179" s="8" t="inlineStr">
+        <is>
           <t>farm-c49b19e235e2b061</t>
-        </is>
-      </c>
-      <c r="B179" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C179" s="8" t="n">
@@ -11826,12 +11826,12 @@
     <row r="180">
       <c r="A180" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B180" s="8" t="inlineStr">
+        <is>
           <t>farm-c49b19e235e2b061</t>
-        </is>
-      </c>
-      <c r="B180" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C180" s="8" t="n">
@@ -11862,12 +11862,12 @@
     <row r="181">
       <c r="A181" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B181" s="8" t="inlineStr">
+        <is>
           <t>farm-c49b19e235e2b061</t>
-        </is>
-      </c>
-      <c r="B181" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
@@ -11898,12 +11898,12 @@
     <row r="182">
       <c r="A182" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B182" s="8" t="inlineStr">
+        <is>
           <t>farm-c49b19e235e2b061</t>
-        </is>
-      </c>
-      <c r="B182" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C182" s="8" t="n">
@@ -11934,12 +11934,12 @@
     <row r="183">
       <c r="A183" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B183" s="8" t="inlineStr">
+        <is>
           <t>farm-c49b19e235e2b061</t>
-        </is>
-      </c>
-      <c r="B183" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
@@ -11970,12 +11970,12 @@
     <row r="184">
       <c r="A184" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B184" s="8" t="inlineStr">
+        <is>
           <t>farm-c49b19e235e2b061</t>
-        </is>
-      </c>
-      <c r="B184" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C184" s="8" t="n">
@@ -12006,12 +12006,12 @@
     <row r="185">
       <c r="A185" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B185" s="8" t="inlineStr">
+        <is>
           <t>farm-c49b19e235e2b061</t>
-        </is>
-      </c>
-      <c r="B185" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
@@ -12042,12 +12042,12 @@
     <row r="186">
       <c r="A186" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B186" s="16" t="inlineStr">
+        <is>
           <t>farm-c49b19e235e2b061</t>
-        </is>
-      </c>
-      <c r="B186" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C186" s="16" t="n">
@@ -12078,12 +12078,12 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
           <t>farm-9a61b6a17f97ba72</t>
-        </is>
-      </c>
-      <c r="B187" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C187" s="4" t="n">
@@ -12114,12 +12114,12 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
           <t>farm-9a61b6a17f97ba72</t>
-        </is>
-      </c>
-      <c r="B188" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C188" s="4" t="n">
@@ -12150,12 +12150,12 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
           <t>farm-9a61b6a17f97ba72</t>
-        </is>
-      </c>
-      <c r="B189" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C189" s="4" t="n">
@@ -12186,12 +12186,12 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
           <t>farm-9a61b6a17f97ba72</t>
-        </is>
-      </c>
-      <c r="B190" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C190" s="4" t="n">
@@ -12222,12 +12222,12 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
           <t>farm-9a61b6a17f97ba72</t>
-        </is>
-      </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C191" s="4" t="n">
@@ -12258,12 +12258,12 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
           <t>farm-9a61b6a17f97ba72</t>
-        </is>
-      </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C192" s="4" t="n">
@@ -12294,12 +12294,12 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
           <t>farm-9a61b6a17f97ba72</t>
-        </is>
-      </c>
-      <c r="B193" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C193" s="4" t="n">
@@ -12330,12 +12330,12 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
           <t>farm-9a61b6a17f97ba72</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C194" s="4" t="n">
@@ -12366,12 +12366,12 @@
     <row r="195">
       <c r="A195" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B195" s="12" t="inlineStr">
+        <is>
           <t>farm-9a61b6a17f97ba72</t>
-        </is>
-      </c>
-      <c r="B195" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C195" s="12" t="n">
@@ -12402,12 +12402,12 @@
     <row r="196">
       <c r="A196" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B196" s="8" t="inlineStr">
+        <is>
           <t>farm-0dbf3bd5fa5b6f36</t>
-        </is>
-      </c>
-      <c r="B196" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C196" s="8" t="n">
@@ -12438,12 +12438,12 @@
     <row r="197">
       <c r="A197" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B197" s="8" t="inlineStr">
+        <is>
           <t>farm-0dbf3bd5fa5b6f36</t>
-        </is>
-      </c>
-      <c r="B197" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C197" s="8" t="n">
@@ -12474,12 +12474,12 @@
     <row r="198">
       <c r="A198" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B198" s="8" t="inlineStr">
+        <is>
           <t>farm-0dbf3bd5fa5b6f36</t>
-        </is>
-      </c>
-      <c r="B198" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C198" s="8" t="n">
@@ -12510,12 +12510,12 @@
     <row r="199">
       <c r="A199" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B199" s="8" t="inlineStr">
+        <is>
           <t>farm-0dbf3bd5fa5b6f36</t>
-        </is>
-      </c>
-      <c r="B199" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C199" s="8" t="n">
@@ -12546,12 +12546,12 @@
     <row r="200">
       <c r="A200" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B200" s="8" t="inlineStr">
+        <is>
           <t>farm-0dbf3bd5fa5b6f36</t>
-        </is>
-      </c>
-      <c r="B200" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C200" s="8" t="n">
@@ -12582,12 +12582,12 @@
     <row r="201">
       <c r="A201" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B201" s="16" t="inlineStr">
+        <is>
           <t>farm-0dbf3bd5fa5b6f36</t>
-        </is>
-      </c>
-      <c r="B201" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C201" s="16" t="n">
@@ -12618,12 +12618,12 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
           <t>farm-3f8574c5694d1cf0</t>
-        </is>
-      </c>
-      <c r="B202" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C202" s="4" t="n">
@@ -12654,12 +12654,12 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
           <t>farm-3f8574c5694d1cf0</t>
-        </is>
-      </c>
-      <c r="B203" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C203" s="4" t="n">
@@ -12690,12 +12690,12 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
           <t>farm-3f8574c5694d1cf0</t>
-        </is>
-      </c>
-      <c r="B204" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C204" s="4" t="n">
@@ -12726,12 +12726,12 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
           <t>farm-3f8574c5694d1cf0</t>
-        </is>
-      </c>
-      <c r="B205" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C205" s="4" t="n">
@@ -12762,12 +12762,12 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
           <t>farm-3f8574c5694d1cf0</t>
-        </is>
-      </c>
-      <c r="B206" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C206" s="4" t="n">
@@ -12798,12 +12798,12 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
           <t>farm-3f8574c5694d1cf0</t>
-        </is>
-      </c>
-      <c r="B207" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C207" s="4" t="n">
@@ -12834,12 +12834,12 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
           <t>farm-3f8574c5694d1cf0</t>
-        </is>
-      </c>
-      <c r="B208" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C208" s="4" t="n">
@@ -12870,12 +12870,12 @@
     <row r="209">
       <c r="A209" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B209" s="12" t="inlineStr">
+        <is>
           <t>farm-3f8574c5694d1cf0</t>
-        </is>
-      </c>
-      <c r="B209" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C209" s="12" t="n">
@@ -12906,12 +12906,12 @@
     <row r="210">
       <c r="A210" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B210" s="8" t="inlineStr">
+        <is>
           <t>farm-b0db552916b2cd10</t>
-        </is>
-      </c>
-      <c r="B210" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C210" s="8" t="n">
@@ -12942,12 +12942,12 @@
     <row r="211">
       <c r="A211" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B211" s="8" t="inlineStr">
+        <is>
           <t>farm-b0db552916b2cd10</t>
-        </is>
-      </c>
-      <c r="B211" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C211" s="8" t="n">
@@ -12978,12 +12978,12 @@
     <row r="212">
       <c r="A212" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B212" s="8" t="inlineStr">
+        <is>
           <t>farm-b0db552916b2cd10</t>
-        </is>
-      </c>
-      <c r="B212" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C212" s="8" t="n">
@@ -13014,12 +13014,12 @@
     <row r="213">
       <c r="A213" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B213" s="8" t="inlineStr">
+        <is>
           <t>farm-b0db552916b2cd10</t>
-        </is>
-      </c>
-      <c r="B213" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C213" s="8" t="n">
@@ -13050,12 +13050,12 @@
     <row r="214">
       <c r="A214" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B214" s="16" t="inlineStr">
+        <is>
           <t>farm-b0db552916b2cd10</t>
-        </is>
-      </c>
-      <c r="B214" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C214" s="16" t="n">
@@ -13086,12 +13086,12 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
           <t>farm-57a8d7f843c38504</t>
-        </is>
-      </c>
-      <c r="B215" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C215" s="4" t="n">
@@ -13122,12 +13122,12 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
           <t>farm-57a8d7f843c38504</t>
-        </is>
-      </c>
-      <c r="B216" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C216" s="4" t="n">
@@ -13158,12 +13158,12 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
           <t>farm-57a8d7f843c38504</t>
-        </is>
-      </c>
-      <c r="B217" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C217" s="4" t="n">
@@ -13194,12 +13194,12 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
           <t>farm-57a8d7f843c38504</t>
-        </is>
-      </c>
-      <c r="B218" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C218" s="4" t="n">
@@ -13230,12 +13230,12 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
           <t>farm-57a8d7f843c38504</t>
-        </is>
-      </c>
-      <c r="B219" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C219" s="4" t="n">
@@ -13266,12 +13266,12 @@
     <row r="220">
       <c r="A220" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B220" s="12" t="inlineStr">
+        <is>
           <t>farm-57a8d7f843c38504</t>
-        </is>
-      </c>
-      <c r="B220" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C220" s="12" t="n">
@@ -13302,12 +13302,12 @@
     <row r="221">
       <c r="A221" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B221" s="8" t="inlineStr">
+        <is>
           <t>farm-856d7e3cc18639c7</t>
-        </is>
-      </c>
-      <c r="B221" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C221" s="8" t="n">
@@ -13338,12 +13338,12 @@
     <row r="222">
       <c r="A222" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B222" s="8" t="inlineStr">
+        <is>
           <t>farm-856d7e3cc18639c7</t>
-        </is>
-      </c>
-      <c r="B222" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C222" s="8" t="n">
@@ -13374,12 +13374,12 @@
     <row r="223">
       <c r="A223" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B223" s="8" t="inlineStr">
+        <is>
           <t>farm-856d7e3cc18639c7</t>
-        </is>
-      </c>
-      <c r="B223" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C223" s="8" t="n">
@@ -13410,12 +13410,12 @@
     <row r="224">
       <c r="A224" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B224" s="8" t="inlineStr">
+        <is>
           <t>farm-856d7e3cc18639c7</t>
-        </is>
-      </c>
-      <c r="B224" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C224" s="8" t="n">
@@ -13450,12 +13450,12 @@
     <row r="225">
       <c r="A225" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B225" s="8" t="inlineStr">
+        <is>
           <t>farm-856d7e3cc18639c7</t>
-        </is>
-      </c>
-      <c r="B225" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C225" s="8" t="n">
@@ -13486,12 +13486,12 @@
     <row r="226">
       <c r="A226" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B226" s="8" t="inlineStr">
+        <is>
           <t>farm-856d7e3cc18639c7</t>
-        </is>
-      </c>
-      <c r="B226" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C226" s="8" t="n">
@@ -13522,12 +13522,12 @@
     <row r="227">
       <c r="A227" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B227" s="8" t="inlineStr">
+        <is>
           <t>farm-856d7e3cc18639c7</t>
-        </is>
-      </c>
-      <c r="B227" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C227" s="8" t="n">
@@ -13562,12 +13562,12 @@
     <row r="228">
       <c r="A228" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B228" s="8" t="inlineStr">
+        <is>
           <t>farm-856d7e3cc18639c7</t>
-        </is>
-      </c>
-      <c r="B228" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C228" s="8" t="n">
@@ -13598,12 +13598,12 @@
     <row r="229">
       <c r="A229" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B229" s="8" t="inlineStr">
+        <is>
           <t>farm-856d7e3cc18639c7</t>
-        </is>
-      </c>
-      <c r="B229" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C229" s="8" t="n">
@@ -13634,12 +13634,12 @@
     <row r="230">
       <c r="A230" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B230" s="16" t="inlineStr">
+        <is>
           <t>farm-856d7e3cc18639c7</t>
-        </is>
-      </c>
-      <c r="B230" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C230" s="16" t="n">
@@ -13674,12 +13674,12 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
           <t>farm-383f63e3f7a7da24</t>
-        </is>
-      </c>
-      <c r="B231" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C231" s="4" t="n">
@@ -13710,12 +13710,12 @@
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
           <t>farm-383f63e3f7a7da24</t>
-        </is>
-      </c>
-      <c r="B232" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C232" s="4" t="n">
@@ -13746,12 +13746,12 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
           <t>farm-383f63e3f7a7da24</t>
-        </is>
-      </c>
-      <c r="B233" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C233" s="4" t="n">
@@ -13782,12 +13782,12 @@
     <row r="234">
       <c r="A234" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B234" s="12" t="inlineStr">
+        <is>
           <t>farm-383f63e3f7a7da24</t>
-        </is>
-      </c>
-      <c r="B234" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C234" s="12" t="n">
@@ -13818,12 +13818,12 @@
     <row r="235">
       <c r="A235" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B235" s="8" t="inlineStr">
+        <is>
           <t>farm-ff3ff9a555d745f4</t>
-        </is>
-      </c>
-      <c r="B235" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C235" s="8" t="n">
@@ -13854,12 +13854,12 @@
     <row r="236">
       <c r="A236" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B236" s="8" t="inlineStr">
+        <is>
           <t>farm-ff3ff9a555d745f4</t>
-        </is>
-      </c>
-      <c r="B236" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C236" s="8" t="n">
@@ -13890,12 +13890,12 @@
     <row r="237">
       <c r="A237" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B237" s="8" t="inlineStr">
+        <is>
           <t>farm-ff3ff9a555d745f4</t>
-        </is>
-      </c>
-      <c r="B237" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C237" s="8" t="n">
@@ -13926,12 +13926,12 @@
     <row r="238">
       <c r="A238" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B238" s="8" t="inlineStr">
+        <is>
           <t>farm-ff3ff9a555d745f4</t>
-        </is>
-      </c>
-      <c r="B238" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C238" s="8" t="n">
@@ -13962,12 +13962,12 @@
     <row r="239">
       <c r="A239" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B239" s="8" t="inlineStr">
+        <is>
           <t>farm-ff3ff9a555d745f4</t>
-        </is>
-      </c>
-      <c r="B239" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C239" s="8" t="n">
@@ -13998,12 +13998,12 @@
     <row r="240">
       <c r="A240" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B240" s="8" t="inlineStr">
+        <is>
           <t>farm-ff3ff9a555d745f4</t>
-        </is>
-      </c>
-      <c r="B240" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C240" s="8" t="n">
@@ -14034,12 +14034,12 @@
     <row r="241">
       <c r="A241" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B241" s="8" t="inlineStr">
+        <is>
           <t>farm-ff3ff9a555d745f4</t>
-        </is>
-      </c>
-      <c r="B241" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C241" s="8" t="n">
@@ -14070,12 +14070,12 @@
     <row r="242">
       <c r="A242" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B242" s="8" t="inlineStr">
+        <is>
           <t>farm-ff3ff9a555d745f4</t>
-        </is>
-      </c>
-      <c r="B242" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C242" s="8" t="n">
@@ -14106,12 +14106,12 @@
     <row r="243">
       <c r="A243" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B243" s="8" t="inlineStr">
+        <is>
           <t>farm-ff3ff9a555d745f4</t>
-        </is>
-      </c>
-      <c r="B243" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C243" s="8" t="n">
@@ -14142,12 +14142,12 @@
     <row r="244">
       <c r="A244" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B244" s="8" t="inlineStr">
+        <is>
           <t>farm-ff3ff9a555d745f4</t>
-        </is>
-      </c>
-      <c r="B244" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C244" s="8" t="n">
@@ -14178,12 +14178,12 @@
     <row r="245">
       <c r="A245" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B245" s="8" t="inlineStr">
+        <is>
           <t>farm-ff3ff9a555d745f4</t>
-        </is>
-      </c>
-      <c r="B245" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C245" s="8" t="n">
@@ -14214,12 +14214,12 @@
     <row r="246">
       <c r="A246" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B246" s="8" t="inlineStr">
+        <is>
           <t>farm-ff3ff9a555d745f4</t>
-        </is>
-      </c>
-      <c r="B246" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C246" s="8" t="n">
@@ -14250,12 +14250,12 @@
     <row r="247">
       <c r="A247" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B247" s="16" t="inlineStr">
+        <is>
           <t>farm-ff3ff9a555d745f4</t>
-        </is>
-      </c>
-      <c r="B247" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C247" s="16" t="n">
@@ -14286,12 +14286,12 @@
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
           <t>farm-5ccdcf7255ce0473</t>
-        </is>
-      </c>
-      <c r="B248" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C248" s="4" t="n">
@@ -14322,12 +14322,12 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
           <t>farm-5ccdcf7255ce0473</t>
-        </is>
-      </c>
-      <c r="B249" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C249" s="4" t="n">
@@ -14358,12 +14358,12 @@
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
           <t>farm-5ccdcf7255ce0473</t>
-        </is>
-      </c>
-      <c r="B250" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C250" s="4" t="n">
@@ -14394,12 +14394,12 @@
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
           <t>farm-5ccdcf7255ce0473</t>
-        </is>
-      </c>
-      <c r="B251" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C251" s="4" t="n">
@@ -14430,12 +14430,12 @@
     <row r="252">
       <c r="A252" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B252" s="12" t="inlineStr">
+        <is>
           <t>farm-5ccdcf7255ce0473</t>
-        </is>
-      </c>
-      <c r="B252" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C252" s="12" t="n">
@@ -14466,12 +14466,12 @@
     <row r="253">
       <c r="A253" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B253" s="8" t="inlineStr">
+        <is>
           <t>farm-2736bad424a20cd6</t>
-        </is>
-      </c>
-      <c r="B253" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C253" s="8" t="n">
@@ -14502,12 +14502,12 @@
     <row r="254">
       <c r="A254" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B254" s="8" t="inlineStr">
+        <is>
           <t>farm-2736bad424a20cd6</t>
-        </is>
-      </c>
-      <c r="B254" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C254" s="8" t="n">
@@ -14538,12 +14538,12 @@
     <row r="255">
       <c r="A255" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B255" s="8" t="inlineStr">
+        <is>
           <t>farm-2736bad424a20cd6</t>
-        </is>
-      </c>
-      <c r="B255" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C255" s="8" t="n">
@@ -14574,12 +14574,12 @@
     <row r="256">
       <c r="A256" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B256" s="8" t="inlineStr">
+        <is>
           <t>farm-2736bad424a20cd6</t>
-        </is>
-      </c>
-      <c r="B256" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C256" s="8" t="n">
@@ -14610,12 +14610,12 @@
     <row r="257">
       <c r="A257" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B257" s="8" t="inlineStr">
+        <is>
           <t>farm-2736bad424a20cd6</t>
-        </is>
-      </c>
-      <c r="B257" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C257" s="8" t="n">
@@ -14646,12 +14646,12 @@
     <row r="258">
       <c r="A258" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B258" s="8" t="inlineStr">
+        <is>
           <t>farm-2736bad424a20cd6</t>
-        </is>
-      </c>
-      <c r="B258" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C258" s="8" t="n">
@@ -14682,12 +14682,12 @@
     <row r="259">
       <c r="A259" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B259" s="16" t="inlineStr">
+        <is>
           <t>farm-2736bad424a20cd6</t>
-        </is>
-      </c>
-      <c r="B259" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C259" s="16" t="n">
@@ -14718,12 +14718,12 @@
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B260" s="4" t="inlineStr">
+        <is>
           <t>farm-639c9d17e71d07f4</t>
-        </is>
-      </c>
-      <c r="B260" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C260" s="4" t="n">
@@ -14754,12 +14754,12 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="inlineStr">
+        <is>
           <t>farm-639c9d17e71d07f4</t>
-        </is>
-      </c>
-      <c r="B261" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C261" s="4" t="n">
@@ -14790,12 +14790,12 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B262" s="4" t="inlineStr">
+        <is>
           <t>farm-639c9d17e71d07f4</t>
-        </is>
-      </c>
-      <c r="B262" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C262" s="4" t="n">
@@ -14826,12 +14826,12 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B263" s="4" t="inlineStr">
+        <is>
           <t>farm-639c9d17e71d07f4</t>
-        </is>
-      </c>
-      <c r="B263" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C263" s="4" t="n">
@@ -14862,12 +14862,12 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
           <t>farm-639c9d17e71d07f4</t>
-        </is>
-      </c>
-      <c r="B264" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C264" s="4" t="n">
@@ -14898,12 +14898,12 @@
     <row r="265">
       <c r="A265" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B265" s="12" t="inlineStr">
+        <is>
           <t>farm-639c9d17e71d07f4</t>
-        </is>
-      </c>
-      <c r="B265" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C265" s="12" t="n">
@@ -14934,12 +14934,12 @@
     <row r="266">
       <c r="A266" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B266" s="8" t="inlineStr">
+        <is>
           <t>farm-1c62e112fe6b88cb</t>
-        </is>
-      </c>
-      <c r="B266" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C266" s="8" t="n">
@@ -14970,12 +14970,12 @@
     <row r="267">
       <c r="A267" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B267" s="8" t="inlineStr">
+        <is>
           <t>farm-1c62e112fe6b88cb</t>
-        </is>
-      </c>
-      <c r="B267" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C267" s="8" t="n">
@@ -15006,12 +15006,12 @@
     <row r="268">
       <c r="A268" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B268" s="8" t="inlineStr">
+        <is>
           <t>farm-1c62e112fe6b88cb</t>
-        </is>
-      </c>
-      <c r="B268" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C268" s="8" t="n">
@@ -15042,12 +15042,12 @@
     <row r="269">
       <c r="A269" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B269" s="8" t="inlineStr">
+        <is>
           <t>farm-1c62e112fe6b88cb</t>
-        </is>
-      </c>
-      <c r="B269" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C269" s="8" t="n">
@@ -15078,12 +15078,12 @@
     <row r="270">
       <c r="A270" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B270" s="8" t="inlineStr">
+        <is>
           <t>farm-1c62e112fe6b88cb</t>
-        </is>
-      </c>
-      <c r="B270" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C270" s="8" t="n">
@@ -15114,12 +15114,12 @@
     <row r="271">
       <c r="A271" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B271" s="16" t="inlineStr">
+        <is>
           <t>farm-1c62e112fe6b88cb</t>
-        </is>
-      </c>
-      <c r="B271" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C271" s="16" t="n">
@@ -15150,12 +15150,12 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
           <t>farm-68cf2cfdbb044e86</t>
-        </is>
-      </c>
-      <c r="B272" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C272" s="4" t="n">
@@ -15186,12 +15186,12 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
           <t>farm-68cf2cfdbb044e86</t>
-        </is>
-      </c>
-      <c r="B273" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C273" s="4" t="n">
@@ -15222,12 +15222,12 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
           <t>farm-68cf2cfdbb044e86</t>
-        </is>
-      </c>
-      <c r="B274" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C274" s="4" t="n">
@@ -15258,12 +15258,12 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
+        <is>
           <t>farm-68cf2cfdbb044e86</t>
-        </is>
-      </c>
-      <c r="B275" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C275" s="4" t="n">
@@ -15294,12 +15294,12 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="inlineStr">
+        <is>
           <t>farm-68cf2cfdbb044e86</t>
-        </is>
-      </c>
-      <c r="B276" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C276" s="4" t="n">
@@ -15330,12 +15330,12 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
           <t>farm-68cf2cfdbb044e86</t>
-        </is>
-      </c>
-      <c r="B277" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C277" s="4" t="n">
@@ -15366,12 +15366,12 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B278" s="4" t="inlineStr">
+        <is>
           <t>farm-68cf2cfdbb044e86</t>
-        </is>
-      </c>
-      <c r="B278" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C278" s="4" t="n">
@@ -15402,12 +15402,12 @@
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
           <t>farm-68cf2cfdbb044e86</t>
-        </is>
-      </c>
-      <c r="B279" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C279" s="4" t="n">
@@ -15438,12 +15438,12 @@
     <row r="280">
       <c r="A280" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B280" s="12" t="inlineStr">
+        <is>
           <t>farm-68cf2cfdbb044e86</t>
-        </is>
-      </c>
-      <c r="B280" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C280" s="12" t="n">
@@ -15474,12 +15474,12 @@
     <row r="281">
       <c r="A281" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B281" s="8" t="inlineStr">
+        <is>
           <t>farm-719054ad3fa7a13a</t>
-        </is>
-      </c>
-      <c r="B281" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C281" s="8" t="n">
@@ -15510,12 +15510,12 @@
     <row r="282">
       <c r="A282" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B282" s="8" t="inlineStr">
+        <is>
           <t>farm-719054ad3fa7a13a</t>
-        </is>
-      </c>
-      <c r="B282" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C282" s="8" t="n">
@@ -15546,12 +15546,12 @@
     <row r="283">
       <c r="A283" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B283" s="8" t="inlineStr">
+        <is>
           <t>farm-719054ad3fa7a13a</t>
-        </is>
-      </c>
-      <c r="B283" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C283" s="8" t="n">
@@ -15582,12 +15582,12 @@
     <row r="284">
       <c r="A284" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B284" s="8" t="inlineStr">
+        <is>
           <t>farm-719054ad3fa7a13a</t>
-        </is>
-      </c>
-      <c r="B284" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C284" s="8" t="n">
@@ -15618,12 +15618,12 @@
     <row r="285">
       <c r="A285" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B285" s="8" t="inlineStr">
+        <is>
           <t>farm-719054ad3fa7a13a</t>
-        </is>
-      </c>
-      <c r="B285" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C285" s="8" t="n">
@@ -15654,12 +15654,12 @@
     <row r="286">
       <c r="A286" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B286" s="16" t="inlineStr">
+        <is>
           <t>farm-719054ad3fa7a13a</t>
-        </is>
-      </c>
-      <c r="B286" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C286" s="16" t="n">
@@ -15690,12 +15690,12 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B287" s="4" t="inlineStr">
+        <is>
           <t>farm-cd1a7ad828e59ca2</t>
-        </is>
-      </c>
-      <c r="B287" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C287" s="4" t="n">
@@ -15726,12 +15726,12 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B288" s="4" t="inlineStr">
+        <is>
           <t>farm-cd1a7ad828e59ca2</t>
-        </is>
-      </c>
-      <c r="B288" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C288" s="4" t="n">
@@ -15762,12 +15762,12 @@
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B289" s="4" t="inlineStr">
+        <is>
           <t>farm-cd1a7ad828e59ca2</t>
-        </is>
-      </c>
-      <c r="B289" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C289" s="4" t="n">
@@ -15798,12 +15798,12 @@
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B290" s="4" t="inlineStr">
+        <is>
           <t>farm-cd1a7ad828e59ca2</t>
-        </is>
-      </c>
-      <c r="B290" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C290" s="4" t="n">
@@ -15834,12 +15834,12 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B291" s="4" t="inlineStr">
+        <is>
           <t>farm-cd1a7ad828e59ca2</t>
-        </is>
-      </c>
-      <c r="B291" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C291" s="4" t="n">
@@ -15870,12 +15870,12 @@
     <row r="292">
       <c r="A292" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B292" s="12" t="inlineStr">
+        <is>
           <t>farm-cd1a7ad828e59ca2</t>
-        </is>
-      </c>
-      <c r="B292" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C292" s="12" t="n">
@@ -15906,12 +15906,12 @@
     <row r="293">
       <c r="A293" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B293" s="8" t="inlineStr">
+        <is>
           <t>farm-ec87e85565cbba3c</t>
-        </is>
-      </c>
-      <c r="B293" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C293" s="8" t="n">
@@ -15942,12 +15942,12 @@
     <row r="294">
       <c r="A294" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B294" s="8" t="inlineStr">
+        <is>
           <t>farm-ec87e85565cbba3c</t>
-        </is>
-      </c>
-      <c r="B294" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C294" s="8" t="n">
@@ -15978,12 +15978,12 @@
     <row r="295">
       <c r="A295" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B295" s="8" t="inlineStr">
+        <is>
           <t>farm-ec87e85565cbba3c</t>
-        </is>
-      </c>
-      <c r="B295" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C295" s="8" t="n">
@@ -16014,12 +16014,12 @@
     <row r="296">
       <c r="A296" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B296" s="8" t="inlineStr">
+        <is>
           <t>farm-ec87e85565cbba3c</t>
-        </is>
-      </c>
-      <c r="B296" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C296" s="8" t="n">
@@ -16050,12 +16050,12 @@
     <row r="297">
       <c r="A297" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B297" s="8" t="inlineStr">
+        <is>
           <t>farm-ec87e85565cbba3c</t>
-        </is>
-      </c>
-      <c r="B297" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C297" s="8" t="n">
@@ -16086,12 +16086,12 @@
     <row r="298">
       <c r="A298" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B298" s="8" t="inlineStr">
+        <is>
           <t>farm-ec87e85565cbba3c</t>
-        </is>
-      </c>
-      <c r="B298" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C298" s="8" t="n">
@@ -16122,12 +16122,12 @@
     <row r="299">
       <c r="A299" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B299" s="8" t="inlineStr">
+        <is>
           <t>farm-ec87e85565cbba3c</t>
-        </is>
-      </c>
-      <c r="B299" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C299" s="8" t="n">
@@ -16158,12 +16158,12 @@
     <row r="300">
       <c r="A300" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B300" s="8" t="inlineStr">
+        <is>
           <t>farm-ec87e85565cbba3c</t>
-        </is>
-      </c>
-      <c r="B300" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C300" s="8" t="n">
@@ -16194,12 +16194,12 @@
     <row r="301">
       <c r="A301" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B301" s="8" t="inlineStr">
+        <is>
           <t>farm-ec87e85565cbba3c</t>
-        </is>
-      </c>
-      <c r="B301" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C301" s="8" t="n">
@@ -16230,12 +16230,12 @@
     <row r="302">
       <c r="A302" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B302" s="16" t="inlineStr">
+        <is>
           <t>farm-ec87e85565cbba3c</t>
-        </is>
-      </c>
-      <c r="B302" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C302" s="16" t="n">
@@ -16266,12 +16266,12 @@
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
           <t>farm-06f2c6829a4bd5fc</t>
-        </is>
-      </c>
-      <c r="B303" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C303" s="4" t="n">
@@ -16302,12 +16302,12 @@
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
           <t>farm-06f2c6829a4bd5fc</t>
-        </is>
-      </c>
-      <c r="B304" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C304" s="4" t="n">
@@ -16338,12 +16338,12 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
+        <is>
           <t>farm-06f2c6829a4bd5fc</t>
-        </is>
-      </c>
-      <c r="B305" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C305" s="4" t="n">
@@ -16374,12 +16374,12 @@
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B306" s="4" t="inlineStr">
+        <is>
           <t>farm-06f2c6829a4bd5fc</t>
-        </is>
-      </c>
-      <c r="B306" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C306" s="4" t="n">
@@ -16410,12 +16410,12 @@
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B307" s="4" t="inlineStr">
+        <is>
           <t>farm-06f2c6829a4bd5fc</t>
-        </is>
-      </c>
-      <c r="B307" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C307" s="4" t="n">
@@ -16446,12 +16446,12 @@
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B308" s="4" t="inlineStr">
+        <is>
           <t>farm-06f2c6829a4bd5fc</t>
-        </is>
-      </c>
-      <c r="B308" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C308" s="4" t="n">
@@ -16482,12 +16482,12 @@
     <row r="309">
       <c r="A309" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B309" s="12" t="inlineStr">
+        <is>
           <t>farm-06f2c6829a4bd5fc</t>
-        </is>
-      </c>
-      <c r="B309" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C309" s="12" t="n">
@@ -16518,12 +16518,12 @@
     <row r="310">
       <c r="A310" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B310" s="8" t="inlineStr">
+        <is>
           <t>farm-05270ec8c18c39ef</t>
-        </is>
-      </c>
-      <c r="B310" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C310" s="8" t="n">
@@ -16554,12 +16554,12 @@
     <row r="311">
       <c r="A311" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B311" s="8" t="inlineStr">
+        <is>
           <t>farm-05270ec8c18c39ef</t>
-        </is>
-      </c>
-      <c r="B311" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C311" s="8" t="n">
@@ -16590,12 +16590,12 @@
     <row r="312">
       <c r="A312" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B312" s="8" t="inlineStr">
+        <is>
           <t>farm-05270ec8c18c39ef</t>
-        </is>
-      </c>
-      <c r="B312" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C312" s="8" t="n">
@@ -16626,12 +16626,12 @@
     <row r="313">
       <c r="A313" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B313" s="16" t="inlineStr">
+        <is>
           <t>farm-05270ec8c18c39ef</t>
-        </is>
-      </c>
-      <c r="B313" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C313" s="16" t="n">
@@ -16662,12 +16662,12 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B314" s="4" t="inlineStr">
+        <is>
           <t>farm-4564e66abc59f856</t>
-        </is>
-      </c>
-      <c r="B314" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C314" s="4" t="n">
@@ -16698,12 +16698,12 @@
     <row r="315">
       <c r="A315" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B315" s="12" t="inlineStr">
+        <is>
           <t>farm-4564e66abc59f856</t>
-        </is>
-      </c>
-      <c r="B315" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C315" s="12" t="n">
@@ -16734,12 +16734,12 @@
     <row r="316">
       <c r="A316" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B316" s="8" t="inlineStr">
+        <is>
           <t>farm-e83db331287bbc87</t>
-        </is>
-      </c>
-      <c r="B316" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C316" s="8" t="n">
@@ -16770,12 +16770,12 @@
     <row r="317">
       <c r="A317" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B317" s="16" t="inlineStr">
+        <is>
           <t>farm-e83db331287bbc87</t>
-        </is>
-      </c>
-      <c r="B317" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C317" s="16" t="n">
@@ -16806,12 +16806,12 @@
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B318" s="4" t="inlineStr">
+        <is>
           <t>farm-ce9a0c36aa3a1370</t>
-        </is>
-      </c>
-      <c r="B318" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C318" s="4" t="n">
@@ -16842,12 +16842,12 @@
     <row r="319">
       <c r="A319" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B319" s="12" t="inlineStr">
+        <is>
           <t>farm-ce9a0c36aa3a1370</t>
-        </is>
-      </c>
-      <c r="B319" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C319" s="12" t="n">
@@ -16878,12 +16878,12 @@
     <row r="320">
       <c r="A320" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B320" s="8" t="inlineStr">
+        <is>
           <t>farm-681881e6608d6b6d</t>
-        </is>
-      </c>
-      <c r="B320" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C320" s="8" t="n">
@@ -16914,12 +16914,12 @@
     <row r="321">
       <c r="A321" s="8" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B321" s="8" t="inlineStr">
+        <is>
           <t>farm-681881e6608d6b6d</t>
-        </is>
-      </c>
-      <c r="B321" s="8" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C321" s="8" t="n">
@@ -16950,12 +16950,12 @@
     <row r="322">
       <c r="A322" s="16" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B322" s="16" t="inlineStr">
+        <is>
           <t>farm-681881e6608d6b6d</t>
-        </is>
-      </c>
-      <c r="B322" s="16" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C322" s="16" t="n">
@@ -16986,12 +16986,12 @@
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B323" s="4" t="inlineStr">
+        <is>
           <t>farm-2de1bf871636377b</t>
-        </is>
-      </c>
-      <c r="B323" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C323" s="4" t="n">
@@ -17022,12 +17022,12 @@
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B324" s="4" t="inlineStr">
+        <is>
           <t>farm-2de1bf871636377b</t>
-        </is>
-      </c>
-      <c r="B324" s="4" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C324" s="4" t="n">
@@ -17058,12 +17058,12 @@
     <row r="325">
       <c r="A325" s="12" t="inlineStr">
         <is>
+          <t>balliang_labels.shp</t>
+        </is>
+      </c>
+      <c r="B325" s="12" t="inlineStr">
+        <is>
           <t>farm-2de1bf871636377b</t>
-        </is>
-      </c>
-      <c r="B325" s="12" t="inlineStr">
-        <is>
-          <t>balliang_labels.shp</t>
         </is>
       </c>
       <c r="C325" s="12" t="n">
